--- a/01_analyses_states/Karnataka/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Karnataka/results/SoIB_summaries.xlsx
@@ -393,16 +393,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2">
-        <v>3.3</v>
+        <v>7.1</v>
       </c>
       <c r="E2">
-        <v>20.2</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="3">
@@ -415,13 +415,13 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3">
-        <v>13.3</v>
+        <v>14.3</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C4">
         <v>37</v>
       </c>
       <c r="D4">
-        <v>46.7</v>
+        <v>42.9</v>
       </c>
       <c r="E4">
-        <v>41.6</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="5">
@@ -456,10 +456,10 @@
         <v>3</v>
       </c>
       <c r="D5">
-        <v>13.3</v>
+        <v>14.3</v>
       </c>
       <c r="E5">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="6">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6">
-        <v>23.3</v>
+        <v>21.4</v>
       </c>
       <c r="E6">
-        <v>7.9</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C7">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C8">
         <v>221</v>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="3">
@@ -693,7 +693,7 @@
         <v>79</v>
       </c>
       <c r="C3">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C4">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5">

--- a/01_analyses_states/Karnataka/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Karnataka/results/SoIB_summaries.xlsx
@@ -393,16 +393,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="E2">
-        <v>19.4</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="3">
@@ -412,16 +412,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D3">
-        <v>10.7</v>
+        <v>14.3</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C4">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D4">
-        <v>53.6</v>
+        <v>42.9</v>
       </c>
       <c r="E4">
-        <v>44.4</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="5">
@@ -453,13 +453,13 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5">
         <v>14.3</v>
       </c>
       <c r="E5">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="6">
@@ -472,13 +472,13 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D6">
         <v>21.4</v>
       </c>
       <c r="E6">
-        <v>8.300000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="7">
@@ -491,7 +491,7 @@
         <v>51</v>
       </c>
       <c r="C7">
-        <v>160</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C8">
         <v>221</v>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="3">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C4">
-        <v>72</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5">
@@ -763,16 +763,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C2">
-        <v>70.90000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E2">
-        <v>80.2</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="3">
@@ -782,16 +782,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3">
-        <v>29.1</v>
+        <v>28.2</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>19.8</v>
+        <v>18.7</v>
       </c>
     </row>
   </sheetData>

--- a/01_analyses_states/Karnataka/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Karnataka/results/SoIB_summaries.xlsx
@@ -393,16 +393,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>7.1</v>
+        <v>18.9</v>
       </c>
       <c r="E2">
-        <v>21.1</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="3">
@@ -412,16 +412,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C3">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D3">
-        <v>14.3</v>
+        <v>32.4</v>
       </c>
       <c r="E3">
-        <v>25.6</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="4">
@@ -434,13 +434,13 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D4">
-        <v>42.9</v>
+        <v>32.4</v>
       </c>
       <c r="E4">
-        <v>41.1</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="5">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D5">
-        <v>14.3</v>
+        <v>5.4</v>
       </c>
       <c r="E5">
-        <v>3.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="6">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>21.4</v>
+        <v>10.8</v>
       </c>
       <c r="E6">
-        <v>8.9</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C7">
-        <v>141</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="C8">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>553</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>452</v>
+        <v>445</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C4">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5">
@@ -763,16 +763,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C2">
-        <v>71.8</v>
+        <v>68</v>
       </c>
       <c r="D2">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E2">
-        <v>81.3</v>
+        <v>74.5</v>
       </c>
     </row>
     <row r="3">
@@ -782,16 +782,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C3">
-        <v>28.2</v>
+        <v>32</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>18.7</v>
+        <v>25.5</v>
       </c>
     </row>
   </sheetData>
